--- a/config/excel/game_tuning.xlsx
+++ b/config/excel/game_tuning.xlsx
@@ -423,12 +423,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1141,6 +1141,66 @@
       <c r="C47" t="inlineStr">
         <is>
           <t>目标帧率(0=不限制)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>stage_monster_base</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>8</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>第1关怪物总数（stages表为权威）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>stage_monster_per_stage</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>每过一关怪物总数+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>stage_type_unlock_interval</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>每N关解锁下一种怪物</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>stage_atk_growth</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>关卡攻击缩放幂次</t>
         </is>
       </c>
     </row>
